--- a/HMS-TAX_Updated/HMS-TAX/bin/Debug/Reports/rpt_po_details.xlsx
+++ b/HMS-TAX_Updated/HMS-TAX/bin/Debug/Reports/rpt_po_details.xlsx
@@ -46,9 +46,6 @@
     <t>Items</t>
   </si>
   <si>
-    <t>Exp</t>
-  </si>
-  <si>
     <t>PO ID</t>
   </si>
   <si>
@@ -62,6 +59,10 @@
   </si>
   <si>
     <t>Purchase Order details</t>
+  </si>
+  <si>
+    <t>Other
+Cost</t>
   </si>
 </sst>
 </file>
@@ -69,7 +70,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -171,9 +172,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -198,11 +199,11 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -217,13 +218,13 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -247,7 +248,7 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -262,6 +263,9 @@
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -575,7 +579,8 @@
     <col min="4" max="4" width="17" style="6" customWidth="1"/>
     <col min="5" max="5" width="11.7109375" style="26" customWidth="1"/>
     <col min="6" max="6" width="19.7109375" style="27" customWidth="1"/>
-    <col min="7" max="8" width="6.7109375" style="17" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" style="17" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" style="17" customWidth="1"/>
     <col min="9" max="9" width="6.7109375" style="14" customWidth="1"/>
     <col min="10" max="10" width="11" style="17" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.5703125" style="17" customWidth="1"/>
@@ -603,7 +608,7 @@
     <row r="2" spans="2:16" customFormat="1" ht="13.15" customHeight="1">
       <c r="B2" s="21"/>
       <c r="C2" s="31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" s="31"/>
       <c r="E2" s="31"/>
@@ -655,18 +660,18 @@
       <c r="M4" s="3"/>
       <c r="N4" s="15"/>
     </row>
-    <row r="5" spans="2:16" customFormat="1" ht="23.45" customHeight="1">
+    <row r="5" spans="2:16" customFormat="1" ht="31.5">
       <c r="B5" s="23" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>9</v>
@@ -674,8 +679,8 @@
       <c r="G5" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="12" t="s">
-        <v>10</v>
+      <c r="H5" s="33" t="s">
+        <v>15</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>4</v>
@@ -690,13 +695,13 @@
         <v>3</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N5" s="13" t="s">
         <v>6</v>
       </c>
       <c r="O5" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
